--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5522-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5522-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{586C9E3F-59D1-49E7-891B-5820674CB6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E11BDE6-2D44-4A60-830C-33EEA3791FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{261E10C3-D8D7-45FD-BDC6-333C009E3E42}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{359505F7-6D71-42C8-A05A-C54BBEB082C9}"/>
   </bookViews>
   <sheets>
     <sheet name="5522-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1505,25 +1505,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F009142-BAEE-4BBB-AC84-23283454892C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7217F9B4-FDF8-4FCE-B218-905DA747D43B}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1551,7 +1551,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1677,7 +1677,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>2024</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2023</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>4.7699999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="41">
         <v>2022</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2021</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>2020</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2019</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <v>2018</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>7.59</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2017</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="41">
         <v>2016</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2015</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="41">
         <v>2014</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2013</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="41">
         <v>2012</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2011</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="41">
         <v>2010</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2009</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="41">
         <v>2008</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2007</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="41">
         <v>2006</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2005</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="41">
         <v>2004</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>2003</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="41">
         <v>2002</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>2001</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="41">
         <v>2000</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>1999</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>9.81</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="41">
         <v>1998</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>1997</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="41" t="s">
         <v>52</v>
       </c>
